--- a/Assets/test260903/test260903.xlsx
+++ b/Assets/test260903/test260903.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_B9B2B4CFFEBC0FA459F3055EF38874C741D70555" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7999DB8D-5A89-4BA9-B02A-0FE882983F24}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Character" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Texture" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Particle" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Layer" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="EyeBlink" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="LipSynch" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="Animation" sheetId="7" r:id="rId10"/>
-    <sheet state="visible" name="Sound" sheetId="8" r:id="rId11"/>
-    <sheet state="visible" name="Param" sheetId="9" r:id="rId12"/>
-    <sheet state="visible" name="ParamTbl{}" sheetId="10" r:id="rId13"/>
-    <sheet state="visible" name="SceneGallery" sheetId="11" r:id="rId14"/>
-    <sheet state="visible" name="Localize" sheetId="12" r:id="rId15"/>
-    <sheet state="visible" name="Macro" sheetId="13" r:id="rId16"/>
+    <sheet name="Character" sheetId="1" r:id="rId1"/>
+    <sheet name="Texture" sheetId="2" r:id="rId2"/>
+    <sheet name="Particle" sheetId="3" r:id="rId3"/>
+    <sheet name="Layer" sheetId="4" r:id="rId4"/>
+    <sheet name="EyeBlink" sheetId="5" r:id="rId5"/>
+    <sheet name="LipSynch" sheetId="6" r:id="rId6"/>
+    <sheet name="Animation" sheetId="7" r:id="rId7"/>
+    <sheet name="Sound" sheetId="8" r:id="rId8"/>
+    <sheet name="Param" sheetId="9" r:id="rId9"/>
+    <sheet name="ParamTbl{}" sheetId="10" r:id="rId10"/>
+    <sheet name="SceneGallery" sheetId="11" r:id="rId11"/>
+    <sheet name="Localize" sheetId="12" r:id="rId12"/>
+    <sheet name="Macro" sheetId="13" r:id="rId13"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId17" roundtripDataChecksum="k4kJvhmNYlUXRIv7kxzmdI6uo4KHYqKu9IL60h+8lcQ="/>
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="190">
   <si>
     <t>Label</t>
   </si>
@@ -264,356 +273,384 @@
     <t>room.jpg</t>
   </si>
   <si>
+    <t>event_001.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter1-1</t>
+  </si>
+  <si>
+    <t>title_chapter0101.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter1-2</t>
+  </si>
+  <si>
+    <t>title_chapter0102.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter1-3</t>
+  </si>
+  <si>
+    <t>title_chapter0103.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter1-4</t>
+  </si>
+  <si>
+    <t>title_chapter0104.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter1-5</t>
+  </si>
+  <si>
+    <t>title_chapter0105.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter1-6</t>
+  </si>
+  <si>
+    <t>title_chapter0106.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter2-1</t>
+  </si>
+  <si>
+    <t>title_chapter0201.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter2-2</t>
+  </si>
+  <si>
+    <t>title_chapter0202.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter2-3</t>
+  </si>
+  <si>
+    <t>title_chapter0203.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter2-4</t>
+  </si>
+  <si>
+    <t>title_chapter0204.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter2-5</t>
+  </si>
+  <si>
+    <t>title_chapter0205.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter2-6</t>
+  </si>
+  <si>
+    <t>title_chapter0206.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter3-1</t>
+  </si>
+  <si>
+    <t>title_chapter0301.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter3-2</t>
+  </si>
+  <si>
+    <t>title_chapter0302.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter3-3</t>
+  </si>
+  <si>
+    <t>title_chapter0303.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter3-4</t>
+  </si>
+  <si>
+    <t>title_chapter0304.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter3-5</t>
+  </si>
+  <si>
+    <t>title_chapter0305.jpg</t>
+  </si>
+  <si>
+    <t>タイトル：Chapter3-6</t>
+  </si>
+  <si>
+    <t>title_chapter0306.jpg</t>
+  </si>
+  <si>
+    <t>IntervalMin</t>
+  </si>
+  <si>
+    <t>IntervalMax</t>
+  </si>
+  <si>
+    <t>RandomDouble</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>Name0</t>
+  </si>
+  <si>
+    <t>Duration0</t>
+  </si>
+  <si>
+    <t>Name1</t>
+  </si>
+  <si>
+    <t>Duration1</t>
+  </si>
+  <si>
+    <t>Name2</t>
+  </si>
+  <si>
+    <t>Duration2</t>
+  </si>
+  <si>
+    <t>Name3</t>
+  </si>
+  <si>
+    <t>Duration3</t>
+  </si>
+  <si>
+    <t>Name4</t>
+  </si>
+  <si>
+    <t>Duration4</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>ScaleVoiceVolume</t>
+  </si>
+  <si>
+    <t>*SampleAnimation</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Angle</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>IntroTime</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>BGM1</t>
+  </si>
+  <si>
+    <t>ドリーミン</t>
+  </si>
+  <si>
+    <t>Bgm</t>
+  </si>
+  <si>
+    <t>dreaming.ogg</t>
+  </si>
+  <si>
+    <t>BGM2</t>
+  </si>
+  <si>
+    <t>不可思議話</t>
+  </si>
+  <si>
+    <t>hukashigibanashi.ogg</t>
+  </si>
+  <si>
+    <t>BGM3</t>
+  </si>
+  <si>
+    <t>変わりゆく街</t>
+  </si>
+  <si>
+    <t>kawariyukumachi.ogg</t>
+  </si>
+  <si>
+    <t>BGM4</t>
+  </si>
+  <si>
+    <t>希望を空へ</t>
+  </si>
+  <si>
+    <t>kibouwosorahe.ogg</t>
+  </si>
+  <si>
+    <t>BGM5</t>
+  </si>
+  <si>
+    <t>music</t>
+  </si>
+  <si>
+    <t>music.ogg</t>
+  </si>
+  <si>
+    <t>BGM6</t>
+  </si>
+  <si>
+    <t>夏の眠り</t>
+  </si>
+  <si>
+    <t>natsunonemuri.ogg</t>
+  </si>
+  <si>
+    <t>BGM7</t>
+  </si>
+  <si>
+    <t>ピクニックに行こう</t>
+  </si>
+  <si>
+    <t>pikunikkuniikou.ogg</t>
+  </si>
+  <si>
+    <t>BGM8</t>
+  </si>
+  <si>
+    <t>線香花火</t>
+  </si>
+  <si>
+    <t>senkouhanabi.ogg</t>
+  </si>
+  <si>
+    <t>電話</t>
+  </si>
+  <si>
+    <t>Se</t>
+  </si>
+  <si>
+    <t>fon001.ogg</t>
+  </si>
+  <si>
+    <t>走る足音</t>
+  </si>
+  <si>
+    <t>Leather_shoes_run.ogg</t>
+  </si>
+  <si>
+    <t>歩く足音</t>
+  </si>
+  <si>
+    <t>Leather_shoes_walk.ogg</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>ScenarioLabel</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Command</t>
+  </si>
+  <si>
+    <t>Arg1</t>
+  </si>
+  <si>
+    <t>Arg2</t>
+  </si>
+  <si>
+    <t>Arg3</t>
+  </si>
+  <si>
+    <t>Arg4</t>
+  </si>
+  <si>
+    <t>Arg5</t>
+  </si>
+  <si>
+    <t>Arg6</t>
+  </si>
+  <si>
+    <t>WaitType</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>PageCtrl</t>
+  </si>
+  <si>
+    <t>Voice</t>
+  </si>
+  <si>
+    <t>WindowType</t>
+  </si>
+  <si>
+    <t>倒れる音</t>
+    <rPh sb="0" eb="1">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>fall.mp3</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Event</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <t>一枚絵</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>event_001.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter1-1</t>
-  </si>
-  <si>
-    <t>title_chapter0101.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter1-2</t>
-  </si>
-  <si>
-    <t>title_chapter0102.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter1-3</t>
-  </si>
-  <si>
-    <t>title_chapter0103.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter1-4</t>
-  </si>
-  <si>
-    <t>title_chapter0104.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter1-5</t>
-  </si>
-  <si>
-    <t>title_chapter0105.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter1-6</t>
-  </si>
-  <si>
-    <t>title_chapter0106.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter2-1</t>
-  </si>
-  <si>
-    <t>title_chapter0201.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter2-2</t>
-  </si>
-  <si>
-    <t>title_chapter0202.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter2-3</t>
-  </si>
-  <si>
-    <t>title_chapter0203.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter2-4</t>
-  </si>
-  <si>
-    <t>title_chapter0204.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter2-5</t>
-  </si>
-  <si>
-    <t>title_chapter0205.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter2-6</t>
-  </si>
-  <si>
-    <t>title_chapter0206.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter3-1</t>
-  </si>
-  <si>
-    <t>title_chapter0301.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter3-2</t>
-  </si>
-  <si>
-    <t>title_chapter0302.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter3-3</t>
-  </si>
-  <si>
-    <t>title_chapter0303.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter3-4</t>
-  </si>
-  <si>
-    <t>title_chapter0304.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter3-5</t>
-  </si>
-  <si>
-    <t>title_chapter0305.jpg</t>
-  </si>
-  <si>
-    <t>タイトル：Chapter3-6</t>
-  </si>
-  <si>
-    <t>title_chapter0306.jpg</t>
-  </si>
-  <si>
-    <t>IntervalMin</t>
-  </si>
-  <si>
-    <t>IntervalMax</t>
-  </si>
-  <si>
-    <t>RandomDouble</t>
-  </si>
-  <si>
-    <t>Tag</t>
-  </si>
-  <si>
-    <t>Name0</t>
-  </si>
-  <si>
-    <t>Duration0</t>
-  </si>
-  <si>
-    <t>Name1</t>
-  </si>
-  <si>
-    <t>Duration1</t>
-  </si>
-  <si>
-    <t>Name2</t>
-  </si>
-  <si>
-    <t>Duration2</t>
-  </si>
-  <si>
-    <t>Name3</t>
-  </si>
-  <si>
-    <t>Duration3</t>
-  </si>
-  <si>
-    <t>Name4</t>
-  </si>
-  <si>
-    <t>Duration4</t>
-  </si>
-  <si>
-    <t>Interval</t>
-  </si>
-  <si>
-    <t>ScaleVoiceVolume</t>
-  </si>
-  <si>
-    <t>*SampleAnimation</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Angle</t>
-  </si>
-  <si>
-    <t>Alpha</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>IntroTime</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>BGM1</t>
-  </si>
-  <si>
-    <t>ドリーミン</t>
-  </si>
-  <si>
-    <t>Bgm</t>
-  </si>
-  <si>
-    <t>dreaming.ogg</t>
-  </si>
-  <si>
-    <t>BGM2</t>
-  </si>
-  <si>
-    <t>不可思議話</t>
-  </si>
-  <si>
-    <t>hukashigibanashi.ogg</t>
-  </si>
-  <si>
-    <t>BGM3</t>
-  </si>
-  <si>
-    <t>変わりゆく街</t>
-  </si>
-  <si>
-    <t>kawariyukumachi.ogg</t>
-  </si>
-  <si>
-    <t>BGM4</t>
-  </si>
-  <si>
-    <t>希望を空へ</t>
-  </si>
-  <si>
-    <t>kibouwosorahe.ogg</t>
-  </si>
-  <si>
-    <t>BGM5</t>
-  </si>
-  <si>
-    <t>music</t>
-  </si>
-  <si>
-    <t>music.ogg</t>
-  </si>
-  <si>
-    <t>BGM6</t>
-  </si>
-  <si>
-    <t>夏の眠り</t>
-  </si>
-  <si>
-    <t>natsunonemuri.ogg</t>
-  </si>
-  <si>
-    <t>BGM7</t>
-  </si>
-  <si>
-    <t>ピクニックに行こう</t>
-  </si>
-  <si>
-    <t>pikunikkuniikou.ogg</t>
-  </si>
-  <si>
-    <t>BGM8</t>
-  </si>
-  <si>
-    <t>線香花火</t>
-  </si>
-  <si>
-    <t>senkouhanabi.ogg</t>
-  </si>
-  <si>
-    <t>電話</t>
-  </si>
-  <si>
-    <t>Se</t>
-  </si>
-  <si>
-    <t>fon001.ogg</t>
-  </si>
-  <si>
-    <t>走る足音</t>
-  </si>
-  <si>
-    <t>Leather_shoes_run.ogg</t>
-  </si>
-  <si>
-    <t>歩く足音</t>
-  </si>
-  <si>
-    <t>Leather_shoes_walk.ogg</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>ScenarioLabel</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Command</t>
-  </si>
-  <si>
-    <t>Arg1</t>
-  </si>
-  <si>
-    <t>Arg2</t>
-  </si>
-  <si>
-    <t>Arg3</t>
-  </si>
-  <si>
-    <t>Arg4</t>
-  </si>
-  <si>
-    <t>Arg5</t>
-  </si>
-  <si>
-    <t>Arg6</t>
-  </si>
-  <si>
-    <t>WaitType</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>PageCtrl</t>
-  </si>
-  <si>
-    <t>Voice</t>
-  </si>
-  <si>
-    <t>WindowType</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -621,88 +658,48 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -892,39 +889,39 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.25"/>
-    <col customWidth="1" min="2" max="2" width="9.63"/>
-    <col customWidth="1" min="3" max="3" width="7.38"/>
-    <col customWidth="1" min="4" max="5" width="2.63"/>
-    <col customWidth="1" min="6" max="6" width="2.5"/>
-    <col customWidth="1" min="7" max="7" width="5.5"/>
-    <col customWidth="1" min="8" max="8" width="5.88"/>
-    <col customWidth="1" min="9" max="9" width="10.25"/>
-    <col customWidth="1" min="10" max="10" width="8.75"/>
-    <col customWidth="1" min="11" max="11" width="14.0"/>
-    <col customWidth="1" min="12" max="12" width="8.13"/>
-    <col customWidth="1" min="13" max="13" width="9.25"/>
-    <col customWidth="1" min="14" max="14" width="13.75"/>
-    <col customWidth="1" min="15" max="15" width="11.0"/>
-    <col customWidth="1" min="16" max="16" width="8.25"/>
-    <col customWidth="1" min="17" max="17" width="8.75"/>
-    <col customWidth="1" min="18" max="18" width="5.0"/>
-    <col customWidth="1" min="19" max="19" width="9.88"/>
-    <col customWidth="1" min="20" max="20" width="8.75"/>
-    <col customWidth="1" min="21" max="26" width="8.0"/>
+    <col min="1" max="1" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" customWidth="1"/>
+    <col min="4" max="5" width="2.6640625" customWidth="1"/>
+    <col min="6" max="6" width="2.44140625" customWidth="1"/>
+    <col min="7" max="7" width="5.44140625" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" customWidth="1"/>
+    <col min="10" max="10" width="8.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" customWidth="1"/>
+    <col min="13" max="13" width="9.21875" customWidth="1"/>
+    <col min="14" max="14" width="13.77734375" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="8.21875" customWidth="1"/>
+    <col min="17" max="17" width="8.77734375" customWidth="1"/>
+    <col min="18" max="18" width="5" customWidth="1"/>
+    <col min="19" max="19" width="9.88671875" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" customWidth="1"/>
+    <col min="21" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:20" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -986,69 +983,69 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="C3" s="2" t="s">
+    <row r="3" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="C4" s="2" t="s">
+    <row r="4" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="C5" s="2" t="s">
+    <row r="5" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="C6" s="2" t="s">
+    <row r="6" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:20" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:20" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:20" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:20" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:20" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:20" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:20" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:20" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:20" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -2034,52 +2031,49 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:A1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="13.0"/>
-    <col customWidth="1" min="7" max="26" width="8.0"/>
+    <col min="1" max="6" width="13" customWidth="1"/>
+    <col min="7" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:1" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
+    <row r="2" spans="1:1" ht="13.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
+    <row r="3" spans="1:1" ht="13.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1"/>
-    <row r="5" ht="13.5" customHeight="1"/>
-    <row r="6" ht="13.5" customHeight="1"/>
-    <row r="7" ht="13.5" customHeight="1"/>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="4" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="6" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="7" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:1" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -3065,53 +3059,50 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:C1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.88"/>
-    <col customWidth="1" min="2" max="2" width="5.0"/>
-    <col customWidth="1" min="3" max="3" width="9.5"/>
-    <col customWidth="1" min="4" max="6" width="8.88"/>
-    <col customWidth="1" min="7" max="26" width="8.0"/>
+    <col min="1" max="1" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="5" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" customWidth="1"/>
+    <col min="4" max="6" width="8.88671875" customWidth="1"/>
+    <col min="7" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:3" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1"/>
-    <row r="3" ht="13.5" customHeight="1"/>
-    <row r="4" ht="13.5" customHeight="1"/>
-    <row r="5" ht="13.5" customHeight="1"/>
-    <row r="6" ht="13.5" customHeight="1"/>
-    <row r="7" ht="13.5" customHeight="1"/>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="2" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="3" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="4" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="6" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="7" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:3" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:3" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -4097,44 +4088,41 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:A1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="13.0"/>
-    <col customWidth="1" min="7" max="26" width="8.0"/>
+    <col min="1" max="6" width="13" customWidth="1"/>
+    <col min="7" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:1" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1"/>
-    <row r="3" ht="13.5" customHeight="1"/>
-    <row r="4" ht="13.5" customHeight="1"/>
-    <row r="5" ht="13.5" customHeight="1"/>
-    <row r="6" ht="13.5" customHeight="1"/>
-    <row r="7" ht="13.5" customHeight="1"/>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="2" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="3" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="4" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="6" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="7" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:1" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:1" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -5120,83 +5108,80 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:L1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="9.25"/>
-    <col customWidth="1" min="2" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="5.13"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="9.21875" customWidth="1"/>
+    <col min="2" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="5.109375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>187</v>
-      </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1"/>
-    <row r="3" ht="13.5" customHeight="1"/>
-    <row r="4" ht="13.5" customHeight="1"/>
-    <row r="5" ht="13.5" customHeight="1"/>
-    <row r="6" ht="13.5" customHeight="1"/>
-    <row r="7" ht="13.5" customHeight="1"/>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="2" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="3" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="4" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="7" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:12" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:12" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -6182,39 +6167,36 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:P1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.5"/>
-    <col customWidth="1" min="2" max="2" width="5.38"/>
-    <col customWidth="1" min="3" max="4" width="2.63"/>
-    <col customWidth="1" min="5" max="5" width="2.5"/>
-    <col customWidth="1" min="6" max="6" width="5.5"/>
-    <col customWidth="1" min="7" max="7" width="5.88"/>
-    <col customWidth="1" min="8" max="8" width="10.25"/>
-    <col customWidth="1" min="9" max="9" width="8.75"/>
-    <col customWidth="1" min="10" max="10" width="8.13"/>
-    <col customWidth="1" min="11" max="11" width="14.0"/>
-    <col customWidth="1" min="12" max="12" width="9.25"/>
-    <col customWidth="1" min="13" max="13" width="13.75"/>
-    <col customWidth="1" min="14" max="14" width="11.0"/>
-    <col customWidth="1" min="15" max="15" width="9.5"/>
-    <col customWidth="1" min="16" max="16" width="11.0"/>
-    <col customWidth="1" min="17" max="26" width="8.0"/>
+    <col min="1" max="1" width="26.44140625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="4" width="2.6640625" customWidth="1"/>
+    <col min="5" max="5" width="2.44140625" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" customWidth="1"/>
+    <col min="7" max="7" width="5.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="9.21875" customWidth="1"/>
+    <col min="13" max="13" width="13.77734375" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.44140625" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:16" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6264,353 +6246,353 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="2" t="s">
+    <row r="13" spans="1:16" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:16" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:16" ht="13.5" customHeight="1">
+      <c r="A16" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A17" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I17" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I18" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A19" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I19" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A20" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I20" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A21" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I21" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A22" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I22" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A23" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I23" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="2" t="s">
+    <row r="24" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A24" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I24" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="2" t="s">
+    <row r="25" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A25" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I25" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="A25" s="2" t="s">
+    <row r="26" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A26" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I26" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="2" t="s">
+    <row r="27" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A27" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I27" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="2" t="s">
+    <row r="28" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I28" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="2" t="s">
+    <row r="29" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A29" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I29" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
-      <c r="A29" s="2" t="s">
+    <row r="30" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A30" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="I30" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A31" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="I31" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A32" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I32" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="A32" s="2" t="s">
+    <row r="33" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A33" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I33" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="A33" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" ht="13.5" customHeight="1"/>
-    <row r="35" ht="13.5" customHeight="1"/>
-    <row r="36" ht="13.5" customHeight="1"/>
-    <row r="37" ht="13.5" customHeight="1"/>
-    <row r="38" ht="13.5" customHeight="1"/>
-    <row r="39" ht="13.5" customHeight="1"/>
-    <row r="40" ht="13.5" customHeight="1"/>
-    <row r="41" ht="13.5" customHeight="1"/>
-    <row r="42" ht="13.5" customHeight="1"/>
-    <row r="43" ht="13.5" customHeight="1"/>
-    <row r="44" ht="13.5" customHeight="1"/>
-    <row r="45" ht="13.5" customHeight="1"/>
-    <row r="46" ht="13.5" customHeight="1"/>
-    <row r="47" ht="13.5" customHeight="1"/>
-    <row r="48" ht="13.5" customHeight="1"/>
+    <row r="34" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="35" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="36" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="37" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="38" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="39" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="40" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="41" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="42" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="43" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="44" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="45" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="46" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="47" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="48" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="49" ht="13.5" customHeight="1"/>
     <row r="50" ht="13.5" customHeight="1"/>
     <row r="51" ht="13.5" customHeight="1"/>
@@ -7564,28 +7546,25 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.63"/>
-    <col customWidth="1" min="2" max="2" width="8.75"/>
-    <col customWidth="1" min="3" max="3" width="9.38"/>
-    <col customWidth="1" min="4" max="6" width="8.63"/>
-    <col customWidth="1" min="7" max="26" width="8.0"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:2" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7593,21 +7572,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1"/>
-    <row r="3" ht="13.5" customHeight="1"/>
-    <row r="4" ht="13.5" customHeight="1"/>
-    <row r="5" ht="13.5" customHeight="1"/>
-    <row r="6" ht="13.5" customHeight="1"/>
-    <row r="7" ht="13.5" customHeight="1"/>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="2" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="3" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="4" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="6" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="7" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -8593,38 +8572,35 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:Q1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.38"/>
-    <col customWidth="1" min="2" max="2" width="12.25"/>
-    <col customWidth="1" min="3" max="4" width="5.38"/>
-    <col customWidth="1" min="5" max="5" width="6.0"/>
-    <col customWidth="1" min="6" max="6" width="9.88"/>
-    <col customWidth="1" min="7" max="8" width="7.0"/>
-    <col customWidth="1" min="9" max="10" width="5.25"/>
-    <col customWidth="1" min="11" max="11" width="5.75"/>
-    <col customWidth="1" min="12" max="12" width="6.63"/>
-    <col customWidth="1" min="13" max="13" width="10.13"/>
-    <col customWidth="1" min="14" max="14" width="11.0"/>
-    <col customWidth="1" min="15" max="15" width="9.88"/>
-    <col customWidth="1" min="16" max="16" width="13.0"/>
-    <col customWidth="1" min="17" max="17" width="5.25"/>
-    <col customWidth="1" min="18" max="26" width="8.0"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" customWidth="1"/>
+    <col min="3" max="4" width="5.33203125" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" customWidth="1"/>
+    <col min="7" max="8" width="7" customWidth="1"/>
+    <col min="9" max="10" width="5.21875" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" customWidth="1"/>
+    <col min="13" max="13" width="10.109375" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="9.88671875" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="5.21875" customWidth="1"/>
+    <col min="18" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:17" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -8677,69 +8653,69 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:17" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>200.0</v>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>200</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" ht="13.5" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="2">
-        <v>-250.0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>190.0</v>
+      <c r="C3" s="1">
+        <v>-250</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>190</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:17" ht="13.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="2">
-        <v>250.0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>190.0</v>
+      <c r="C4" s="1">
+        <v>250</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>190</v>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1"/>
-    <row r="6" ht="13.5" customHeight="1"/>
-    <row r="7" ht="13.5" customHeight="1"/>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="6" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="7" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:17" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:17" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -9725,99 +9701,96 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.63"/>
-    <col customWidth="1" min="2" max="2" width="10.13"/>
-    <col customWidth="1" min="3" max="3" width="10.5"/>
-    <col customWidth="1" min="4" max="4" width="13.63"/>
-    <col customWidth="1" min="5" max="5" width="4.38"/>
-    <col customWidth="1" min="6" max="6" width="7.0"/>
-    <col customWidth="1" min="7" max="7" width="9.25"/>
-    <col customWidth="1" min="8" max="8" width="7.0"/>
-    <col customWidth="1" min="9" max="9" width="9.25"/>
-    <col customWidth="1" min="10" max="10" width="7.0"/>
-    <col customWidth="1" min="11" max="11" width="9.25"/>
-    <col customWidth="1" min="12" max="12" width="7.0"/>
-    <col customWidth="1" min="13" max="14" width="9.25"/>
-    <col customWidth="1" min="15" max="15" width="7.0"/>
-    <col customWidth="1" min="16" max="26" width="8.0"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" customWidth="1"/>
+    <col min="6" max="6" width="7" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="9.21875" customWidth="1"/>
+    <col min="12" max="12" width="7" customWidth="1"/>
+    <col min="13" max="14" width="9.21875" customWidth="1"/>
+    <col min="15" max="15" width="7" customWidth="1"/>
+    <col min="16" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:15" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>130</v>
-      </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1"/>
-    <row r="3" ht="13.5" customHeight="1"/>
-    <row r="4" ht="13.5" customHeight="1"/>
-    <row r="5" ht="13.5" customHeight="1"/>
-    <row r="6" ht="13.5" customHeight="1"/>
-    <row r="7" ht="13.5" customHeight="1"/>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="2" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="3" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="4" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="6" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="7" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:15" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -10803,39 +10776,36 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:O1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.63"/>
-    <col customWidth="1" min="2" max="2" width="5.38"/>
-    <col customWidth="1" min="3" max="3" width="7.38"/>
-    <col customWidth="1" min="4" max="4" width="4.38"/>
-    <col customWidth="1" min="5" max="5" width="16.88"/>
-    <col customWidth="1" min="6" max="6" width="7.0"/>
-    <col customWidth="1" min="7" max="7" width="9.25"/>
-    <col customWidth="1" min="8" max="8" width="7.0"/>
-    <col customWidth="1" min="9" max="9" width="9.25"/>
-    <col customWidth="1" min="10" max="10" width="7.0"/>
-    <col customWidth="1" min="11" max="11" width="9.25"/>
-    <col customWidth="1" min="12" max="12" width="7.0"/>
-    <col customWidth="1" min="13" max="13" width="9.25"/>
-    <col customWidth="1" min="14" max="14" width="7.0"/>
-    <col customWidth="1" min="15" max="15" width="9.25"/>
-    <col customWidth="1" min="16" max="26" width="8.0"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="6" max="6" width="7" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="9.21875" customWidth="1"/>
+    <col min="12" max="12" width="7" customWidth="1"/>
+    <col min="13" max="13" width="9.21875" customWidth="1"/>
+    <col min="14" max="14" width="7" customWidth="1"/>
+    <col min="15" max="15" width="9.21875" customWidth="1"/>
+    <col min="16" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:15" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10843,60 +10813,60 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>130</v>
-      </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1"/>
-    <row r="3" ht="13.5" customHeight="1"/>
-    <row r="4" ht="13.5" customHeight="1"/>
-    <row r="5" ht="13.5" customHeight="1"/>
-    <row r="6" ht="13.5" customHeight="1"/>
-    <row r="7" ht="13.5" customHeight="1"/>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="2" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="3" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="4" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="6" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="7" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:15" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:15" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -11882,105 +11852,102 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.88"/>
-    <col customWidth="1" min="2" max="6" width="8.38"/>
-    <col customWidth="1" min="7" max="26" width="8.0"/>
+    <col min="1" max="1" width="21.88671875" customWidth="1"/>
+    <col min="2" max="6" width="8.33203125" customWidth="1"/>
+    <col min="7" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
+    <row r="2" spans="1:6" ht="13.5" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1">
         <v>0.5</v>
       </c>
       <c r="D2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1">
         <v>1.5</v>
       </c>
       <c r="F2" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
+    <row r="3" spans="1:6" ht="13.5" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1">
-        <v>-50.0</v>
+        <v>-50</v>
       </c>
       <c r="C4" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>360.0</v>
+        <v>360</v>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -11991,16 +11958,16 @@
         <v>1.2</v>
       </c>
       <c r="D6" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -12011,43 +11978,43 @@
         <v>1.2</v>
       </c>
       <c r="D7" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B8" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="C8" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:6" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -13033,35 +13000,32 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.88"/>
-    <col customWidth="1" min="2" max="2" width="16.63"/>
-    <col customWidth="1" min="3" max="3" width="5.38"/>
-    <col customWidth="1" min="4" max="4" width="8.75"/>
-    <col customWidth="1" min="5" max="5" width="9.13"/>
-    <col customWidth="1" min="6" max="6" width="7.38"/>
-    <col customWidth="1" min="7" max="26" width="8.0"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" customWidth="1"/>
+    <col min="7" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:6" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -13070,161 +13034,171 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>139</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>143</v>
+      <c r="D3" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="4" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>146</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>149</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A6" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>152</v>
       </c>
+      <c r="C6" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>155</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>156</v>
+      </c>
     </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>158</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>159</v>
+      </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="9" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="C9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="10" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>164</v>
       </c>
+      <c r="D10" s="1" t="s">
+        <v>165</v>
+      </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="2" t="s">
+    <row r="11" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C11" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A12" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C12" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>171</v>
+    <row r="13" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>187</v>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:6" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -14210,29 +14184,26 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:D1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.63"/>
-    <col customWidth="1" min="2" max="2" width="5.38"/>
-    <col customWidth="1" min="3" max="3" width="5.88"/>
-    <col customWidth="1" min="4" max="4" width="8.13"/>
-    <col customWidth="1" min="5" max="6" width="8.88"/>
-    <col customWidth="1" min="7" max="26" width="8.0"/>
+    <col min="1" max="1" width="5.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" customWidth="1"/>
+    <col min="5" max="6" width="8.88671875" customWidth="1"/>
+    <col min="7" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:4" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14240,27 +14211,27 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1"/>
-    <row r="3" ht="13.5" customHeight="1"/>
-    <row r="4" ht="13.5" customHeight="1"/>
-    <row r="5" ht="13.5" customHeight="1"/>
-    <row r="6" ht="13.5" customHeight="1"/>
-    <row r="7" ht="13.5" customHeight="1"/>
-    <row r="8" ht="13.5" customHeight="1"/>
-    <row r="9" ht="13.5" customHeight="1"/>
-    <row r="10" ht="13.5" customHeight="1"/>
-    <row r="11" ht="13.5" customHeight="1"/>
-    <row r="12" ht="13.5" customHeight="1"/>
-    <row r="13" ht="13.5" customHeight="1"/>
-    <row r="14" ht="13.5" customHeight="1"/>
-    <row r="15" ht="13.5" customHeight="1"/>
-    <row r="16" ht="13.5" customHeight="1"/>
+    <row r="2" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="3" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="4" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="6" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="7" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="9" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="10" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="11" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="12" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="13" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="14" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:4" ht="13.5" customHeight="1"/>
+    <row r="16" spans="1:4" ht="13.5" customHeight="1"/>
     <row r="17" ht="13.5" customHeight="1"/>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
@@ -15246,9 +15217,8 @@
     <row r="999" ht="13.5" customHeight="1"/>
     <row r="1000" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/test260903.xlsx
+++ b/Assets/test260903/test260903.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="266">
   <si>
     <t>Label</t>
   </si>
@@ -617,6 +617,234 @@
   <si>
     <t>一枚絵</t>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>背景：旅客機の機内</t>
+  </si>
+  <si>
+    <t>airplane.png</t>
+  </si>
+  <si>
+    <t>背景：空港</t>
+  </si>
+  <si>
+    <t>airport.png</t>
+  </si>
+  <si>
+    <t>背景：車内（ハマー）</t>
+  </si>
+  <si>
+    <t>car_hummer.png</t>
+  </si>
+  <si>
+    <t>背景：街中</t>
+  </si>
+  <si>
+    <t>street.png</t>
+  </si>
+  <si>
+    <t>背景：街中（車体爆発）</t>
+  </si>
+  <si>
+    <t>street_explosion.png</t>
+  </si>
+  <si>
+    <t>背景：レストラン</t>
+  </si>
+  <si>
+    <t>restaurant.png</t>
+  </si>
+  <si>
+    <t>背景：スラム街</t>
+  </si>
+  <si>
+    <t>slum.png</t>
+  </si>
+  <si>
+    <t>背景：廃屋</t>
+  </si>
+  <si>
+    <t>haioku.png</t>
+  </si>
+  <si>
+    <t>背景：武器庫</t>
+  </si>
+  <si>
+    <t>armory.png</t>
+  </si>
+  <si>
+    <t>背景：車内（ベンツ）</t>
+  </si>
+  <si>
+    <t>car_benz.png</t>
+  </si>
+  <si>
+    <t>背景：会社のエントランス（戦闘後）</t>
+  </si>
+  <si>
+    <t>office_entrance.png</t>
+  </si>
+  <si>
+    <t>背景：プライベートジェットの機内</t>
+  </si>
+  <si>
+    <t>jet.png</t>
+  </si>
+  <si>
+    <t>BGM_不穏</t>
+  </si>
+  <si>
+    <t>不穏</t>
+  </si>
+  <si>
+    <t>fuon.mp3</t>
+  </si>
+  <si>
+    <t>BGM_日常コミカル</t>
+  </si>
+  <si>
+    <t>なんでしょう？</t>
+  </si>
+  <si>
+    <t>nandeshou.mp3</t>
+  </si>
+  <si>
+    <t>BGM_緊迫</t>
+  </si>
+  <si>
+    <t>Devil Disaster</t>
+  </si>
+  <si>
+    <t>devil_disaster.mp3</t>
+  </si>
+  <si>
+    <t>BGM_バトル</t>
+  </si>
+  <si>
+    <t>危機</t>
+  </si>
+  <si>
+    <t>kiki.mp3</t>
+  </si>
+  <si>
+    <t>BGM_スラム</t>
+  </si>
+  <si>
+    <t>アジア歓楽街</t>
+  </si>
+  <si>
+    <t>asia_kanrakugai.mp3</t>
+  </si>
+  <si>
+    <t>BGM_しんみり</t>
+  </si>
+  <si>
+    <t>神隠しの真相</t>
+  </si>
+  <si>
+    <t>kamikakushinoshinsou.mp3</t>
+  </si>
+  <si>
+    <t>BGM_決意</t>
+  </si>
+  <si>
+    <t>Determination</t>
+  </si>
+  <si>
+    <t>determination.mp3</t>
+  </si>
+  <si>
+    <t>殴打（ゲンコツ）</t>
+  </si>
+  <si>
+    <t>punch_light.mp3</t>
+  </si>
+  <si>
+    <t>殴打</t>
+  </si>
+  <si>
+    <t>punch_heavy.mp3</t>
+  </si>
+  <si>
+    <t>銃声（単発）</t>
+  </si>
+  <si>
+    <t>gun_shot.mp3</t>
+  </si>
+  <si>
+    <t>銃撃戦（連射）</t>
+  </si>
+  <si>
+    <t>gun_fight.mp3</t>
+  </si>
+  <si>
+    <t>銃を構える</t>
+  </si>
+  <si>
+    <t>gun_cock.mp3</t>
+  </si>
+  <si>
+    <t>爆発</t>
+  </si>
+  <si>
+    <t>explosion.mp3</t>
+  </si>
+  <si>
+    <t>車のドア</t>
+  </si>
+  <si>
+    <t>car_door.mp3</t>
+  </si>
+  <si>
+    <t>車の走行（急発進）</t>
+  </si>
+  <si>
+    <t>car_start.mp3</t>
+  </si>
+  <si>
+    <t>急ブレーキ（タイヤ音）</t>
+  </si>
+  <si>
+    <t>car_skid.mp3</t>
+  </si>
+  <si>
+    <t>車の衝突</t>
+  </si>
+  <si>
+    <t>car_crash.mp3</t>
+  </si>
+  <si>
+    <t>ガラスが割れる</t>
+  </si>
+  <si>
+    <t>glass_break.mp3</t>
+  </si>
+  <si>
+    <t>扉を開ける</t>
+  </si>
+  <si>
+    <t>door_open.mp3</t>
+  </si>
+  <si>
+    <t>機内環境音</t>
+  </si>
+  <si>
+    <t>Ambience</t>
+  </si>
+  <si>
+    <t>airplane_ambience.mp3</t>
+  </si>
+  <si>
+    <t>炎が燃える音</t>
+  </si>
+  <si>
+    <t>fire.mp3</t>
+  </si>
+  <si>
+    <t>車の走行</t>
+  </si>
+  <si>
+    <t>car_drive.mp3</t>
   </si>
 </sst>
 </file>
@@ -6579,18 +6807,138 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="35" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="36" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="37" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="38" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="39" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="40" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="41" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="42" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="43" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="44" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="45" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="46" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="35" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A41" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
     <row r="47" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="48" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="49" ht="13.5" customHeight="1"/>
@@ -13197,28 +13545,272 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="13.5" customHeight="1"/>
-    <row r="15" spans="1:6" ht="13.5" customHeight="1"/>
-    <row r="16" spans="1:6" ht="13.5" customHeight="1"/>
-    <row r="17" ht="13.5" customHeight="1"/>
-    <row r="18" ht="13.5" customHeight="1"/>
-    <row r="19" ht="13.5" customHeight="1"/>
-    <row r="20" ht="13.5" customHeight="1"/>
-    <row r="21" ht="13.5" customHeight="1"/>
-    <row r="22" ht="13.5" customHeight="1"/>
-    <row r="23" ht="13.5" customHeight="1"/>
-    <row r="24" ht="13.5" customHeight="1"/>
-    <row r="25" ht="13.5" customHeight="1"/>
-    <row r="26" ht="13.5" customHeight="1"/>
-    <row r="27" ht="13.5" customHeight="1"/>
-    <row r="28" ht="13.5" customHeight="1"/>
-    <row r="29" ht="13.5" customHeight="1"/>
-    <row r="30" ht="13.5" customHeight="1"/>
-    <row r="31" ht="13.5" customHeight="1"/>
-    <row r="32" ht="13.5" customHeight="1"/>
-    <row r="33" ht="13.5" customHeight="1"/>
-    <row r="34" ht="13.5" customHeight="1"/>
-    <row r="35" ht="13.5" customHeight="1"/>
-    <row r="36" ht="13.5" customHeight="1"/>
+    <row r="15" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" ht="13.5" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" ht="13.5" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21" ht="13.5" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="23" ht="13.5" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="24" ht="13.5" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" ht="13.5" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" ht="13.5" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="27" ht="13.5" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="28" ht="13.5" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" ht="13.5" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30" ht="13.5" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="31" ht="13.5" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" ht="13.5" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="33" ht="13.5" customHeight="1">
+      <c r="A33" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="34" ht="13.5" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35" ht="13.5" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="36" ht="13.5" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
     <row r="37" ht="13.5" customHeight="1"/>
     <row r="38" ht="13.5" customHeight="1"/>
     <row r="39" ht="13.5" customHeight="1"/>

--- a/Assets/test260903/test260903.xlsx
+++ b/Assets/test260903/test260903.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="278">
   <si>
     <t>Label</t>
   </si>
@@ -845,6 +845,42 @@
   </si>
   <si>
     <t>car_drive.mp3</t>
+  </si>
+  <si>
+    <t>鈴野美鈴</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_normal.png</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_happy.png</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_angry.png</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_sad.png</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_tere.png</t>
+  </si>
+  <si>
+    <t>結城奏</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_normal.png</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_happy.png</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_angry.png</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_sad.png</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_tere.png</t>
   </si>
 </sst>
 </file>
@@ -1265,16 +1301,92 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="13.5" customHeight="1"/>
-    <row r="9" spans="1:20" ht="13.5" customHeight="1"/>
-    <row r="10" spans="1:20" ht="13.5" customHeight="1"/>
-    <row r="11" spans="1:20" ht="13.5" customHeight="1"/>
-    <row r="12" spans="1:20" ht="13.5" customHeight="1"/>
-    <row r="13" spans="1:20" ht="13.5" customHeight="1"/>
-    <row r="14" spans="1:20" ht="13.5" customHeight="1"/>
-    <row r="15" spans="1:20" ht="13.5" customHeight="1"/>
-    <row r="16" spans="1:20" ht="13.5" customHeight="1"/>
-    <row r="17" ht="13.5" customHeight="1"/>
+    <row r="8" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="13.5" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="13.5" customHeight="1">
+      <c r="C16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="C17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
     <row r="18" ht="13.5" customHeight="1"/>
     <row r="19" ht="13.5" customHeight="1"/>
     <row r="20" ht="13.5" customHeight="1"/>

--- a/Assets/test260903/test260903.xlsx
+++ b/Assets/test260903/test260903.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="367">
   <si>
     <t>Label</t>
   </si>
@@ -881,6 +881,273 @@
   </si>
   <si>
     <t>kanade/003_yuki_tere.png</t>
+  </si>
+  <si>
+    <t>目閉じ</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_sleep.png</t>
+  </si>
+  <si>
+    <t>通常（通信エフェクト）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_normal_comm.png</t>
+  </si>
+  <si>
+    <t>喜び（通信エフェクト）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_happy_comm.png</t>
+  </si>
+  <si>
+    <t>怒り（通信エフェクト）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_angry_comm.png</t>
+  </si>
+  <si>
+    <t>悲しみ（通信エフェクト）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_sad_comm.png</t>
+  </si>
+  <si>
+    <t>喜び（炭化）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_happy_burnt.png</t>
+  </si>
+  <si>
+    <t>悲しみ（炭化）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_sad_burnt.png</t>
+  </si>
+  <si>
+    <t>叔父</t>
+  </si>
+  <si>
+    <t>怯え</t>
+  </si>
+  <si>
+    <t>oji/002_oji_fear.png</t>
+  </si>
+  <si>
+    <t>逆上</t>
+  </si>
+  <si>
+    <t>oji/002_oji_rage.png</t>
+  </si>
+  <si>
+    <t>弱気</t>
+  </si>
+  <si>
+    <t>oji/002_oji_weak.png</t>
+  </si>
+  <si>
+    <t>師匠</t>
+  </si>
+  <si>
+    <t>shisho/002_shisho_normal.png</t>
+  </si>
+  <si>
+    <t>笑い</t>
+  </si>
+  <si>
+    <t>shisho/002_shisho_laugh.png</t>
+  </si>
+  <si>
+    <t>襲撃者</t>
+  </si>
+  <si>
+    <t>負傷</t>
+  </si>
+  <si>
+    <t>russian/002_russian_hurt.png</t>
+  </si>
+  <si>
+    <t>白蛇の男</t>
+  </si>
+  <si>
+    <t>hakuja/002_hakuja_normal.png</t>
+  </si>
+  <si>
+    <t>hakuja/002_hakuja_hurt.png</t>
+  </si>
+  <si>
+    <t>店長</t>
+  </si>
+  <si>
+    <t>tencho/002_tencho_fear.png</t>
+  </si>
+  <si>
+    <t>砂塚浩二</t>
+  </si>
+  <si>
+    <t>sunazuka/003_sunazuka_normal.png</t>
+  </si>
+  <si>
+    <t>険しい</t>
+  </si>
+  <si>
+    <t>sunazuka/003_sunazuka_stern.png</t>
+  </si>
+  <si>
+    <t>14年後</t>
+  </si>
+  <si>
+    <t>sunazuka/003_sunazuka_old_normal.png</t>
+  </si>
+  <si>
+    <t>謎の男</t>
+  </si>
+  <si>
+    <t>背景：通学路（3章・夕方）</t>
+  </si>
+  <si>
+    <t>tsugakuro_ch3_evening.png</t>
+  </si>
+  <si>
+    <t>背景：住宅街（夕方）</t>
+  </si>
+  <si>
+    <t>residential_evening.png</t>
+  </si>
+  <si>
+    <t>背景：鉄製の机と椅子しかない部屋</t>
+  </si>
+  <si>
+    <t>cell.png</t>
+  </si>
+  <si>
+    <t>背景：アルバム</t>
+  </si>
+  <si>
+    <t>album.png</t>
+  </si>
+  <si>
+    <t>背景：浜辺（夜・岩あり）</t>
+  </si>
+  <si>
+    <t>beach_night_stone.png</t>
+  </si>
+  <si>
+    <t>背景：浜辺（夜）</t>
+  </si>
+  <si>
+    <t>beach_night.png</t>
+  </si>
+  <si>
+    <t>背景：施設内の部屋（朝）</t>
+  </si>
+  <si>
+    <t>facility_room.png</t>
+  </si>
+  <si>
+    <t>背景：砂浜の発射台</t>
+  </si>
+  <si>
+    <t>launch_pad.png</t>
+  </si>
+  <si>
+    <t>背景：砂浜の発射台（焼け跡）</t>
+  </si>
+  <si>
+    <t>launch_pad_burnt.png</t>
+  </si>
+  <si>
+    <t>背景：管制室</t>
+  </si>
+  <si>
+    <t>control_room.png</t>
+  </si>
+  <si>
+    <t>背景：医務室</t>
+  </si>
+  <si>
+    <t>infirmary.png</t>
+  </si>
+  <si>
+    <t>背景：喫茶店</t>
+  </si>
+  <si>
+    <t>cafe.png</t>
+  </si>
+  <si>
+    <t>一枚絵：美鈴の寝顔</t>
+  </si>
+  <si>
+    <t>event_002.jpg</t>
+  </si>
+  <si>
+    <t>一枚絵：窓越しの奏</t>
+  </si>
+  <si>
+    <t>event_003.jpg</t>
+  </si>
+  <si>
+    <t>BGM_クライマックス</t>
+  </si>
+  <si>
+    <t>Will you still cry?</t>
+  </si>
+  <si>
+    <t>will_you_still_cry.mp3</t>
+  </si>
+  <si>
+    <t>プラズマ音</t>
+  </si>
+  <si>
+    <t>plasma.mp3</t>
+  </si>
+  <si>
+    <t>ビーム音</t>
+  </si>
+  <si>
+    <t>beam.mp3</t>
+  </si>
+  <si>
+    <t>機械の駆動音（歯車）</t>
+  </si>
+  <si>
+    <t>machine_gear.mp3</t>
+  </si>
+  <si>
+    <t>歓声・拍手</t>
+  </si>
+  <si>
+    <t>cheer.mp3</t>
+  </si>
+  <si>
+    <t>体が崩れる音</t>
+  </si>
+  <si>
+    <t>crumble.mp3</t>
+  </si>
+  <si>
+    <t>波の音</t>
+  </si>
+  <si>
+    <t>wave.mp3</t>
+  </si>
+  <si>
+    <t>時計の秒針</t>
+  </si>
+  <si>
+    <t>clock_tick.mp3</t>
+  </si>
+  <si>
+    <t>喫茶店の環境音</t>
+  </si>
+  <si>
+    <t>cafe_ambience.mp3</t>
+  </si>
+  <si>
+    <t>雑踏</t>
+  </si>
+  <si>
+    <t>crowd.mp3</t>
   </si>
 </sst>
 </file>
@@ -1388,26 +1655,193 @@
       </c>
     </row>
     <row r="18" ht="13.5" customHeight="1"/>
-    <row r="19" ht="13.5" customHeight="1"/>
-    <row r="20" ht="13.5" customHeight="1"/>
-    <row r="21" ht="13.5" customHeight="1"/>
-    <row r="22" ht="13.5" customHeight="1"/>
-    <row r="23" ht="13.5" customHeight="1"/>
-    <row r="24" ht="13.5" customHeight="1"/>
-    <row r="25" ht="13.5" customHeight="1"/>
-    <row r="26" ht="13.5" customHeight="1"/>
-    <row r="27" ht="13.5" customHeight="1"/>
-    <row r="28" ht="13.5" customHeight="1"/>
-    <row r="29" ht="13.5" customHeight="1"/>
-    <row r="30" ht="13.5" customHeight="1"/>
-    <row r="31" ht="13.5" customHeight="1"/>
-    <row r="32" ht="13.5" customHeight="1"/>
-    <row r="33" ht="13.5" customHeight="1"/>
-    <row r="34" ht="13.5" customHeight="1"/>
-    <row r="35" ht="13.5" customHeight="1"/>
-    <row r="36" ht="13.5" customHeight="1"/>
-    <row r="37" ht="13.5" customHeight="1"/>
-    <row r="38" ht="13.5" customHeight="1"/>
+    <row r="19" ht="13.5" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="20" ht="13.5" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" ht="13.5" customHeight="1">
+      <c r="C21" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="22" ht="13.5" customHeight="1">
+      <c r="C22" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="23" ht="13.5" customHeight="1">
+      <c r="C23" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24" ht="13.5" customHeight="1">
+      <c r="C24" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25" ht="13.5" customHeight="1">
+      <c r="C25" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="26" ht="13.5" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="27" ht="13.5" customHeight="1">
+      <c r="C27" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="28" ht="13.5" customHeight="1">
+      <c r="C28" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="29" ht="13.5" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" ht="13.5" customHeight="1">
+      <c r="C30" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31" ht="13.5" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="32" ht="13.5" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="33" ht="13.5" customHeight="1">
+      <c r="C33" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="34" ht="13.5" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="35" ht="13.5" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="36" ht="13.5" customHeight="1">
+      <c r="C36" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="37" ht="13.5" customHeight="1">
+      <c r="C37" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="38" ht="13.5" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
     <row r="39" ht="13.5" customHeight="1"/>
     <row r="40" ht="13.5" customHeight="1"/>
     <row r="41" ht="13.5" customHeight="1"/>
@@ -7052,20 +7486,160 @@
       </c>
     </row>
     <row r="47" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="48" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="49" ht="13.5" customHeight="1"/>
-    <row r="50" ht="13.5" customHeight="1"/>
-    <row r="51" ht="13.5" customHeight="1"/>
-    <row r="52" ht="13.5" customHeight="1"/>
-    <row r="53" ht="13.5" customHeight="1"/>
-    <row r="54" ht="13.5" customHeight="1"/>
-    <row r="55" ht="13.5" customHeight="1"/>
-    <row r="56" ht="13.5" customHeight="1"/>
-    <row r="57" ht="13.5" customHeight="1"/>
-    <row r="58" ht="13.5" customHeight="1"/>
-    <row r="59" ht="13.5" customHeight="1"/>
-    <row r="60" ht="13.5" customHeight="1"/>
-    <row r="61" ht="13.5" customHeight="1"/>
+    <row r="48" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A48" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="49" ht="13.5" customHeight="1">
+      <c r="A49" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="50" ht="13.5" customHeight="1">
+      <c r="A50" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="51" ht="13.5" customHeight="1">
+      <c r="A51" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="52" ht="13.5" customHeight="1">
+      <c r="A52" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="53" ht="13.5" customHeight="1">
+      <c r="A53" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="54" ht="13.5" customHeight="1">
+      <c r="A54" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="55" ht="13.5" customHeight="1">
+      <c r="A55" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="56" ht="13.5" customHeight="1">
+      <c r="A56" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="57" ht="13.5" customHeight="1">
+      <c r="A57" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="58" ht="13.5" customHeight="1">
+      <c r="A58" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="59" ht="13.5" customHeight="1">
+      <c r="A59" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="60" ht="13.5" customHeight="1">
+      <c r="A60" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="61" ht="13.5" customHeight="1">
+      <c r="A61" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
     <row r="62" ht="13.5" customHeight="1"/>
     <row r="63" ht="13.5" customHeight="1"/>
     <row r="64" ht="13.5" customHeight="1"/>
@@ -13924,16 +14498,125 @@
       </c>
     </row>
     <row r="37" ht="13.5" customHeight="1"/>
-    <row r="38" ht="13.5" customHeight="1"/>
-    <row r="39" ht="13.5" customHeight="1"/>
-    <row r="40" ht="13.5" customHeight="1"/>
-    <row r="41" ht="13.5" customHeight="1"/>
-    <row r="42" ht="13.5" customHeight="1"/>
-    <row r="43" ht="13.5" customHeight="1"/>
-    <row r="44" ht="13.5" customHeight="1"/>
-    <row r="45" ht="13.5" customHeight="1"/>
-    <row r="46" ht="13.5" customHeight="1"/>
-    <row r="47" ht="13.5" customHeight="1"/>
+    <row r="38" ht="13.5" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E38" s="1">
+        <v>10.847</v>
+      </c>
+    </row>
+    <row r="39" ht="13.5" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="40" ht="13.5" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="41" ht="13.5" customHeight="1">
+      <c r="A41" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="42" ht="13.5" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="43" ht="13.5" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="44" ht="13.5" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="45" ht="13.5" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="46" ht="13.5" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" ht="13.5" customHeight="1">
+      <c r="A47" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
     <row r="48" ht="13.5" customHeight="1"/>
     <row r="49" ht="13.5" customHeight="1"/>
     <row r="50" ht="13.5" customHeight="1"/>

--- a/Assets/test260903/test260903.xlsx
+++ b/Assets/test260903/test260903.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_B9B2B4CFFEBC0FA459F3055EF38874C741D70555" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7999DB8D-5A89-4BA9-B02A-0FE882983F24}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_B9B2B4CFFEBC0FA459F3055EF38874C741D70555" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A78CD8B-68B8-44DE-A2E8-A014FD50A4CF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -691,463 +691,468 @@
     <t>jet.png</t>
   </si>
   <si>
+    <t>不穏</t>
+  </si>
+  <si>
+    <t>fuon.mp3</t>
+  </si>
+  <si>
+    <t>なんでしょう？</t>
+  </si>
+  <si>
+    <t>nandeshou.mp3</t>
+  </si>
+  <si>
+    <t>Devil Disaster</t>
+  </si>
+  <si>
+    <t>devil_disaster.mp3</t>
+  </si>
+  <si>
+    <t>危機</t>
+  </si>
+  <si>
+    <t>kiki.mp3</t>
+  </si>
+  <si>
+    <t>BGM_スラム</t>
+  </si>
+  <si>
+    <t>アジア歓楽街</t>
+  </si>
+  <si>
+    <t>asia_kanrakugai.mp3</t>
+  </si>
+  <si>
+    <t>BGM_しんみり</t>
+  </si>
+  <si>
+    <t>神隠しの真相</t>
+  </si>
+  <si>
+    <t>kamikakushinoshinsou.mp3</t>
+  </si>
+  <si>
+    <t>BGM_決意</t>
+  </si>
+  <si>
+    <t>Determination</t>
+  </si>
+  <si>
+    <t>determination.mp3</t>
+  </si>
+  <si>
+    <t>殴打（ゲンコツ）</t>
+  </si>
+  <si>
+    <t>punch_light.mp3</t>
+  </si>
+  <si>
+    <t>殴打</t>
+  </si>
+  <si>
+    <t>punch_heavy.mp3</t>
+  </si>
+  <si>
+    <t>銃声（単発）</t>
+  </si>
+  <si>
+    <t>gun_shot.mp3</t>
+  </si>
+  <si>
+    <t>銃撃戦（連射）</t>
+  </si>
+  <si>
+    <t>gun_fight.mp3</t>
+  </si>
+  <si>
+    <t>銃を構える</t>
+  </si>
+  <si>
+    <t>gun_cock.mp3</t>
+  </si>
+  <si>
+    <t>爆発</t>
+  </si>
+  <si>
+    <t>explosion.mp3</t>
+  </si>
+  <si>
+    <t>車のドア</t>
+  </si>
+  <si>
+    <t>car_door.mp3</t>
+  </si>
+  <si>
+    <t>車の走行（急発進）</t>
+  </si>
+  <si>
+    <t>car_start.mp3</t>
+  </si>
+  <si>
+    <t>急ブレーキ（タイヤ音）</t>
+  </si>
+  <si>
+    <t>car_skid.mp3</t>
+  </si>
+  <si>
+    <t>車の衝突</t>
+  </si>
+  <si>
+    <t>car_crash.mp3</t>
+  </si>
+  <si>
+    <t>ガラスが割れる</t>
+  </si>
+  <si>
+    <t>glass_break.mp3</t>
+  </si>
+  <si>
+    <t>扉を開ける</t>
+  </si>
+  <si>
+    <t>door_open.mp3</t>
+  </si>
+  <si>
+    <t>機内環境音</t>
+  </si>
+  <si>
+    <t>Ambience</t>
+  </si>
+  <si>
+    <t>airplane_ambience.mp3</t>
+  </si>
+  <si>
+    <t>炎が燃える音</t>
+  </si>
+  <si>
+    <t>fire.mp3</t>
+  </si>
+  <si>
+    <t>車の走行</t>
+  </si>
+  <si>
+    <t>car_drive.mp3</t>
+  </si>
+  <si>
+    <t>鈴野美鈴</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_normal.png</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_happy.png</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_angry.png</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_sad.png</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_tere.png</t>
+  </si>
+  <si>
+    <t>結城奏</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_normal.png</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_happy.png</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_angry.png</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_sad.png</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_tere.png</t>
+  </si>
+  <si>
+    <t>目閉じ</t>
+  </si>
+  <si>
+    <t>mirei/002_suzuno_sleep.png</t>
+  </si>
+  <si>
+    <t>通常（通信エフェクト）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_normal_comm.png</t>
+  </si>
+  <si>
+    <t>喜び（通信エフェクト）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_happy_comm.png</t>
+  </si>
+  <si>
+    <t>怒り（通信エフェクト）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_angry_comm.png</t>
+  </si>
+  <si>
+    <t>悲しみ（通信エフェクト）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_sad_comm.png</t>
+  </si>
+  <si>
+    <t>喜び（炭化）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_happy_burnt.png</t>
+  </si>
+  <si>
+    <t>悲しみ（炭化）</t>
+  </si>
+  <si>
+    <t>kanade/003_yuki_sad_burnt.png</t>
+  </si>
+  <si>
+    <t>叔父</t>
+  </si>
+  <si>
+    <t>怯え</t>
+  </si>
+  <si>
+    <t>oji/002_oji_fear.png</t>
+  </si>
+  <si>
+    <t>逆上</t>
+  </si>
+  <si>
+    <t>oji/002_oji_rage.png</t>
+  </si>
+  <si>
+    <t>弱気</t>
+  </si>
+  <si>
+    <t>oji/002_oji_weak.png</t>
+  </si>
+  <si>
+    <t>師匠</t>
+  </si>
+  <si>
+    <t>shisho/002_shisho_normal.png</t>
+  </si>
+  <si>
+    <t>笑い</t>
+  </si>
+  <si>
+    <t>shisho/002_shisho_laugh.png</t>
+  </si>
+  <si>
+    <t>襲撃者</t>
+  </si>
+  <si>
+    <t>負傷</t>
+  </si>
+  <si>
+    <t>russian/002_russian_hurt.png</t>
+  </si>
+  <si>
+    <t>白蛇の男</t>
+  </si>
+  <si>
+    <t>hakuja/002_hakuja_normal.png</t>
+  </si>
+  <si>
+    <t>hakuja/002_hakuja_hurt.png</t>
+  </si>
+  <si>
+    <t>店長</t>
+  </si>
+  <si>
+    <t>tencho/002_tencho_fear.png</t>
+  </si>
+  <si>
+    <t>砂塚浩二</t>
+  </si>
+  <si>
+    <t>sunazuka/003_sunazuka_normal.png</t>
+  </si>
+  <si>
+    <t>険しい</t>
+  </si>
+  <si>
+    <t>sunazuka/003_sunazuka_stern.png</t>
+  </si>
+  <si>
+    <t>14年後</t>
+  </si>
+  <si>
+    <t>sunazuka/003_sunazuka_old_normal.png</t>
+  </si>
+  <si>
+    <t>謎の男</t>
+  </si>
+  <si>
+    <t>tsugakuro_ch3_evening.png</t>
+  </si>
+  <si>
+    <t>背景：住宅街（夕方）</t>
+  </si>
+  <si>
+    <t>residential_evening.png</t>
+  </si>
+  <si>
+    <t>背景：鉄製の机と椅子しかない部屋</t>
+  </si>
+  <si>
+    <t>cell.png</t>
+  </si>
+  <si>
+    <t>背景：アルバム</t>
+  </si>
+  <si>
+    <t>album.png</t>
+  </si>
+  <si>
+    <t>背景：浜辺（夜・岩あり）</t>
+  </si>
+  <si>
+    <t>beach_night_stone.png</t>
+  </si>
+  <si>
+    <t>背景：浜辺（夜）</t>
+  </si>
+  <si>
+    <t>beach_night.png</t>
+  </si>
+  <si>
+    <t>背景：施設内の部屋（朝）</t>
+  </si>
+  <si>
+    <t>facility_room.png</t>
+  </si>
+  <si>
+    <t>背景：砂浜の発射台</t>
+  </si>
+  <si>
+    <t>launch_pad.png</t>
+  </si>
+  <si>
+    <t>背景：砂浜の発射台（焼け跡）</t>
+  </si>
+  <si>
+    <t>launch_pad_burnt.png</t>
+  </si>
+  <si>
+    <t>背景：管制室</t>
+  </si>
+  <si>
+    <t>control_room.png</t>
+  </si>
+  <si>
+    <t>背景：医務室</t>
+  </si>
+  <si>
+    <t>infirmary.png</t>
+  </si>
+  <si>
+    <t>背景：喫茶店</t>
+  </si>
+  <si>
+    <t>cafe.png</t>
+  </si>
+  <si>
+    <t>一枚絵：美鈴の寝顔</t>
+  </si>
+  <si>
+    <t>event_002.jpg</t>
+  </si>
+  <si>
+    <t>一枚絵：窓越しの奏</t>
+  </si>
+  <si>
+    <t>event_003.jpg</t>
+  </si>
+  <si>
+    <t>BGM_クライマックス</t>
+  </si>
+  <si>
+    <t>Will you still cry?</t>
+  </si>
+  <si>
+    <t>will_you_still_cry.mp3</t>
+  </si>
+  <si>
+    <t>プラズマ音</t>
+  </si>
+  <si>
+    <t>plasma.mp3</t>
+  </si>
+  <si>
+    <t>ビーム音</t>
+  </si>
+  <si>
+    <t>beam.mp3</t>
+  </si>
+  <si>
+    <t>機械の駆動音（歯車）</t>
+  </si>
+  <si>
+    <t>machine_gear.mp3</t>
+  </si>
+  <si>
+    <t>歓声・拍手</t>
+  </si>
+  <si>
+    <t>cheer.mp3</t>
+  </si>
+  <si>
+    <t>体が崩れる音</t>
+  </si>
+  <si>
+    <t>crumble.mp3</t>
+  </si>
+  <si>
+    <t>波の音</t>
+  </si>
+  <si>
+    <t>wave.mp3</t>
+  </si>
+  <si>
+    <t>時計の秒針</t>
+  </si>
+  <si>
+    <t>clock_tick.mp3</t>
+  </si>
+  <si>
+    <t>喫茶店の環境音</t>
+  </si>
+  <si>
+    <t>cafe_ambience.mp3</t>
+  </si>
+  <si>
+    <t>雑踏</t>
+  </si>
+  <si>
+    <t>crowd.mp3</t>
+  </si>
+  <si>
     <t>BGM_不穏</t>
-  </si>
-  <si>
-    <t>不穏</t>
-  </si>
-  <si>
-    <t>fuon.mp3</t>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>BGM_日常コミカル</t>
-  </si>
-  <si>
-    <t>なんでしょう？</t>
-  </si>
-  <si>
-    <t>nandeshou.mp3</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BGM_バトル</t>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>BGM_緊迫</t>
-  </si>
-  <si>
-    <t>Devil Disaster</t>
-  </si>
-  <si>
-    <t>devil_disaster.mp3</t>
-  </si>
-  <si>
-    <t>BGM_バトル</t>
-  </si>
-  <si>
-    <t>危機</t>
-  </si>
-  <si>
-    <t>kiki.mp3</t>
-  </si>
-  <si>
-    <t>BGM_スラム</t>
-  </si>
-  <si>
-    <t>アジア歓楽街</t>
-  </si>
-  <si>
-    <t>asia_kanrakugai.mp3</t>
-  </si>
-  <si>
-    <t>BGM_しんみり</t>
-  </si>
-  <si>
-    <t>神隠しの真相</t>
-  </si>
-  <si>
-    <t>kamikakushinoshinsou.mp3</t>
-  </si>
-  <si>
-    <t>BGM_決意</t>
-  </si>
-  <si>
-    <t>Determination</t>
-  </si>
-  <si>
-    <t>determination.mp3</t>
-  </si>
-  <si>
-    <t>殴打（ゲンコツ）</t>
-  </si>
-  <si>
-    <t>punch_light.mp3</t>
-  </si>
-  <si>
-    <t>殴打</t>
-  </si>
-  <si>
-    <t>punch_heavy.mp3</t>
-  </si>
-  <si>
-    <t>銃声（単発）</t>
-  </si>
-  <si>
-    <t>gun_shot.mp3</t>
-  </si>
-  <si>
-    <t>銃撃戦（連射）</t>
-  </si>
-  <si>
-    <t>gun_fight.mp3</t>
-  </si>
-  <si>
-    <t>銃を構える</t>
-  </si>
-  <si>
-    <t>gun_cock.mp3</t>
-  </si>
-  <si>
-    <t>爆発</t>
-  </si>
-  <si>
-    <t>explosion.mp3</t>
-  </si>
-  <si>
-    <t>車のドア</t>
-  </si>
-  <si>
-    <t>car_door.mp3</t>
-  </si>
-  <si>
-    <t>車の走行（急発進）</t>
-  </si>
-  <si>
-    <t>car_start.mp3</t>
-  </si>
-  <si>
-    <t>急ブレーキ（タイヤ音）</t>
-  </si>
-  <si>
-    <t>car_skid.mp3</t>
-  </si>
-  <si>
-    <t>車の衝突</t>
-  </si>
-  <si>
-    <t>car_crash.mp3</t>
-  </si>
-  <si>
-    <t>ガラスが割れる</t>
-  </si>
-  <si>
-    <t>glass_break.mp3</t>
-  </si>
-  <si>
-    <t>扉を開ける</t>
-  </si>
-  <si>
-    <t>door_open.mp3</t>
-  </si>
-  <si>
-    <t>機内環境音</t>
-  </si>
-  <si>
-    <t>Ambience</t>
-  </si>
-  <si>
-    <t>airplane_ambience.mp3</t>
-  </si>
-  <si>
-    <t>炎が燃える音</t>
-  </si>
-  <si>
-    <t>fire.mp3</t>
-  </si>
-  <si>
-    <t>車の走行</t>
-  </si>
-  <si>
-    <t>car_drive.mp3</t>
-  </si>
-  <si>
-    <t>鈴野美鈴</t>
-  </si>
-  <si>
-    <t>mirei/002_suzuno_normal.png</t>
-  </si>
-  <si>
-    <t>mirei/002_suzuno_happy.png</t>
-  </si>
-  <si>
-    <t>mirei/002_suzuno_angry.png</t>
-  </si>
-  <si>
-    <t>mirei/002_suzuno_sad.png</t>
-  </si>
-  <si>
-    <t>mirei/002_suzuno_tere.png</t>
-  </si>
-  <si>
-    <t>結城奏</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_normal.png</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_happy.png</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_angry.png</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_sad.png</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_tere.png</t>
-  </si>
-  <si>
-    <t>目閉じ</t>
-  </si>
-  <si>
-    <t>mirei/002_suzuno_sleep.png</t>
-  </si>
-  <si>
-    <t>通常（通信エフェクト）</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_normal_comm.png</t>
-  </si>
-  <si>
-    <t>喜び（通信エフェクト）</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_happy_comm.png</t>
-  </si>
-  <si>
-    <t>怒り（通信エフェクト）</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_angry_comm.png</t>
-  </si>
-  <si>
-    <t>悲しみ（通信エフェクト）</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_sad_comm.png</t>
-  </si>
-  <si>
-    <t>喜び（炭化）</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_happy_burnt.png</t>
-  </si>
-  <si>
-    <t>悲しみ（炭化）</t>
-  </si>
-  <si>
-    <t>kanade/003_yuki_sad_burnt.png</t>
-  </si>
-  <si>
-    <t>叔父</t>
-  </si>
-  <si>
-    <t>怯え</t>
-  </si>
-  <si>
-    <t>oji/002_oji_fear.png</t>
-  </si>
-  <si>
-    <t>逆上</t>
-  </si>
-  <si>
-    <t>oji/002_oji_rage.png</t>
-  </si>
-  <si>
-    <t>弱気</t>
-  </si>
-  <si>
-    <t>oji/002_oji_weak.png</t>
-  </si>
-  <si>
-    <t>師匠</t>
-  </si>
-  <si>
-    <t>shisho/002_shisho_normal.png</t>
-  </si>
-  <si>
-    <t>笑い</t>
-  </si>
-  <si>
-    <t>shisho/002_shisho_laugh.png</t>
-  </si>
-  <si>
-    <t>襲撃者</t>
-  </si>
-  <si>
-    <t>負傷</t>
-  </si>
-  <si>
-    <t>russian/002_russian_hurt.png</t>
-  </si>
-  <si>
-    <t>白蛇の男</t>
-  </si>
-  <si>
-    <t>hakuja/002_hakuja_normal.png</t>
-  </si>
-  <si>
-    <t>hakuja/002_hakuja_hurt.png</t>
-  </si>
-  <si>
-    <t>店長</t>
-  </si>
-  <si>
-    <t>tencho/002_tencho_fear.png</t>
-  </si>
-  <si>
-    <t>砂塚浩二</t>
-  </si>
-  <si>
-    <t>sunazuka/003_sunazuka_normal.png</t>
-  </si>
-  <si>
-    <t>険しい</t>
-  </si>
-  <si>
-    <t>sunazuka/003_sunazuka_stern.png</t>
-  </si>
-  <si>
-    <t>14年後</t>
-  </si>
-  <si>
-    <t>sunazuka/003_sunazuka_old_normal.png</t>
-  </si>
-  <si>
-    <t>謎の男</t>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>背景：通学路（3章・夕方）</t>
-  </si>
-  <si>
-    <t>tsugakuro_ch3_evening.png</t>
-  </si>
-  <si>
-    <t>背景：住宅街（夕方）</t>
-  </si>
-  <si>
-    <t>residential_evening.png</t>
-  </si>
-  <si>
-    <t>背景：鉄製の机と椅子しかない部屋</t>
-  </si>
-  <si>
-    <t>cell.png</t>
-  </si>
-  <si>
-    <t>背景：アルバム</t>
-  </si>
-  <si>
-    <t>album.png</t>
-  </si>
-  <si>
-    <t>背景：浜辺（夜・岩あり）</t>
-  </si>
-  <si>
-    <t>beach_night_stone.png</t>
-  </si>
-  <si>
-    <t>背景：浜辺（夜）</t>
-  </si>
-  <si>
-    <t>beach_night.png</t>
-  </si>
-  <si>
-    <t>背景：施設内の部屋（朝）</t>
-  </si>
-  <si>
-    <t>facility_room.png</t>
-  </si>
-  <si>
-    <t>背景：砂浜の発射台</t>
-  </si>
-  <si>
-    <t>launch_pad.png</t>
-  </si>
-  <si>
-    <t>背景：砂浜の発射台（焼け跡）</t>
-  </si>
-  <si>
-    <t>launch_pad_burnt.png</t>
-  </si>
-  <si>
-    <t>背景：管制室</t>
-  </si>
-  <si>
-    <t>control_room.png</t>
-  </si>
-  <si>
-    <t>背景：医務室</t>
-  </si>
-  <si>
-    <t>infirmary.png</t>
-  </si>
-  <si>
-    <t>背景：喫茶店</t>
-  </si>
-  <si>
-    <t>cafe.png</t>
-  </si>
-  <si>
-    <t>一枚絵：美鈴の寝顔</t>
-  </si>
-  <si>
-    <t>event_002.jpg</t>
-  </si>
-  <si>
-    <t>一枚絵：窓越しの奏</t>
-  </si>
-  <si>
-    <t>event_003.jpg</t>
-  </si>
-  <si>
-    <t>BGM_クライマックス</t>
-  </si>
-  <si>
-    <t>Will you still cry?</t>
-  </si>
-  <si>
-    <t>will_you_still_cry.mp3</t>
-  </si>
-  <si>
-    <t>プラズマ音</t>
-  </si>
-  <si>
-    <t>plasma.mp3</t>
-  </si>
-  <si>
-    <t>ビーム音</t>
-  </si>
-  <si>
-    <t>beam.mp3</t>
-  </si>
-  <si>
-    <t>機械の駆動音（歯車）</t>
-  </si>
-  <si>
-    <t>machine_gear.mp3</t>
-  </si>
-  <si>
-    <t>歓声・拍手</t>
-  </si>
-  <si>
-    <t>cheer.mp3</t>
-  </si>
-  <si>
-    <t>体が崩れる音</t>
-  </si>
-  <si>
-    <t>crumble.mp3</t>
-  </si>
-  <si>
-    <t>波の音</t>
-  </si>
-  <si>
-    <t>wave.mp3</t>
-  </si>
-  <si>
-    <t>時計の秒針</t>
-  </si>
-  <si>
-    <t>clock_tick.mp3</t>
-  </si>
-  <si>
-    <t>喫茶店の環境音</t>
-  </si>
-  <si>
-    <t>cafe_ambience.mp3</t>
-  </si>
-  <si>
-    <t>雑踏</t>
-  </si>
-  <si>
-    <t>crowd.mp3</t>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -1570,13 +1575,13 @@
     </row>
     <row r="8" spans="1:20" ht="13.5" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="13.5" customHeight="1">
@@ -1584,7 +1589,7 @@
         <v>52</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="13.5" customHeight="1">
@@ -1592,7 +1597,7 @@
         <v>57</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="13.5" customHeight="1">
@@ -1600,7 +1605,7 @@
         <v>61</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="13.5" customHeight="1">
@@ -1608,18 +1613,18 @@
         <v>64</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="13.5" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="13.5" customHeight="1">
@@ -1627,7 +1632,7 @@
         <v>52</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="13.5" customHeight="1">
@@ -1635,7 +1640,7 @@
         <v>57</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="13.5" customHeight="1">
@@ -1643,215 +1648,215 @@
         <v>61</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="13.5" customHeight="1">
       <c r="C17" s="1" t="s">
         <v>64</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1"/>
-    <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C19" s="1" t="s">
+    <row r="21" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C21" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="1" t="s">
+    <row r="22" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C22" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="C21" s="1" t="s">
+    <row r="23" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C23" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="C22" s="1" t="s">
+    <row r="24" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C24" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1">
-      <c r="C23" s="1" t="s">
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C25" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
-      <c r="C24" s="1" t="s">
+    <row r="26" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A26" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>289</v>
       </c>
+      <c r="J26" s="1" t="s">
+        <v>290</v>
+      </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="C25" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="J25" s="1" t="s">
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C27" s="1" t="s">
         <v>291</v>
       </c>
+      <c r="J27" s="1" t="s">
+        <v>292</v>
+      </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C26" s="1" t="s">
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C28" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="C27" s="1" t="s">
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A29" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="28" ht="13.5" customHeight="1">
-      <c r="C28" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="29" ht="13.5" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C30" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>300</v>
       </c>
+      <c r="J31" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="C30" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="J30" s="1" t="s">
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A32" s="1" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C33" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A35" s="1" t="s">
         <v>307</v>
-      </c>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="C33" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J35" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C36" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1">
+      <c r="C37" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="C36" s="1" t="s">
+    <row r="38" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A38" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="C37" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
-    <row r="39" ht="13.5" customHeight="1"/>
-    <row r="40" ht="13.5" customHeight="1"/>
-    <row r="41" ht="13.5" customHeight="1"/>
-    <row r="42" ht="13.5" customHeight="1"/>
-    <row r="43" ht="13.5" customHeight="1"/>
-    <row r="44" ht="13.5" customHeight="1"/>
-    <row r="45" ht="13.5" customHeight="1"/>
-    <row r="46" ht="13.5" customHeight="1"/>
-    <row r="47" ht="13.5" customHeight="1"/>
-    <row r="48" ht="13.5" customHeight="1"/>
+    <row r="39" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="40" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="41" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="42" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="43" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="44" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="45" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="46" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="47" spans="1:10" ht="13.5" customHeight="1"/>
+    <row r="48" spans="1:10" ht="13.5" customHeight="1"/>
     <row r="49" ht="13.5" customHeight="1"/>
     <row r="50" ht="13.5" customHeight="1"/>
     <row r="51" ht="13.5" customHeight="1"/>
@@ -7488,161 +7493,161 @@
     <row r="47" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="48" spans="1:9" ht="13.5" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>318</v>
+        <v>366</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
-    <row r="49" ht="13.5" customHeight="1">
+    <row r="49" spans="1:9" ht="13.5" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
-    <row r="50" ht="13.5" customHeight="1">
+    <row r="50" spans="1:9" ht="13.5" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
-    <row r="51" ht="13.5" customHeight="1">
+    <row r="51" spans="1:9" ht="13.5" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
+    <row r="52" spans="1:9" ht="13.5" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
-    <row r="53" ht="13.5" customHeight="1">
+    <row r="53" spans="1:9" ht="13.5" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
-    <row r="54" ht="13.5" customHeight="1">
+    <row r="54" spans="1:9" ht="13.5" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
-    <row r="55" ht="13.5" customHeight="1">
+    <row r="55" spans="1:9" ht="13.5" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
-    <row r="56" ht="13.5" customHeight="1">
+    <row r="56" spans="1:9" ht="13.5" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
-    <row r="57" ht="13.5" customHeight="1">
+    <row r="57" spans="1:9" ht="13.5" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
-    <row r="58" ht="13.5" customHeight="1">
+    <row r="58" spans="1:9" ht="13.5" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
-    <row r="59" ht="13.5" customHeight="1">
+    <row r="59" spans="1:9" ht="13.5" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
-    <row r="60" ht="13.5" customHeight="1">
+    <row r="60" spans="1:9" ht="13.5" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>188</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
-    <row r="61" ht="13.5" customHeight="1">
+    <row r="61" spans="1:9" ht="13.5" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>188</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
-    <row r="62" ht="13.5" customHeight="1"/>
-    <row r="63" ht="13.5" customHeight="1"/>
-    <row r="64" ht="13.5" customHeight="1"/>
+    <row r="62" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="63" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="64" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="65" ht="13.5" customHeight="1"/>
     <row r="66" ht="13.5" customHeight="1"/>
     <row r="67" ht="13.5" customHeight="1"/>
@@ -14233,391 +14238,391 @@
     <row r="14" spans="1:6" ht="13.5" customHeight="1"/>
     <row r="15" spans="1:6" ht="13.5" customHeight="1">
       <c r="A15" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>215</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="13.5" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>217</v>
+        <v>363</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" spans="1:4" ht="13.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>220</v>
+        <v>365</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1">
+    <row r="18" spans="1:4" ht="13.5" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>223</v>
+        <v>364</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="19" ht="13.5" customHeight="1">
+    <row r="19" spans="1:4" ht="13.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1">
+    <row r="20" spans="1:4" ht="13.5" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="21" ht="13.5" customHeight="1">
+    <row r="21" spans="1:4" ht="13.5" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1">
+    <row r="22" spans="1:4" ht="13.5" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1">
+    <row r="23" spans="1:4" ht="13.5" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1">
+    <row r="24" spans="1:4" ht="13.5" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="25" ht="13.5" customHeight="1">
+    <row r="25" spans="1:4" ht="13.5" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1">
+    <row r="26" spans="1:4" ht="13.5" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
-    <row r="27" ht="13.5" customHeight="1">
+    <row r="27" spans="1:4" ht="13.5" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1">
+    <row r="28" spans="1:4" ht="13.5" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
+    <row r="29" spans="1:4" ht="13.5" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1">
+    <row r="30" spans="1:4" ht="13.5" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1">
+    <row r="31" spans="1:4" ht="13.5" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
-    <row r="32" ht="13.5" customHeight="1">
+    <row r="32" spans="1:4" ht="13.5" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1">
+    <row r="33" spans="1:6" ht="13.5" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A35" s="1" t="s">
         <v>258</v>
       </c>
+      <c r="C35" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C34" s="1" t="s">
+    <row r="36" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A36" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>261</v>
-      </c>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>265</v>
       </c>
       <c r="F36" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" ht="13.5" customHeight="1"/>
-    <row r="38" ht="13.5" customHeight="1">
+    <row r="37" spans="1:6" ht="13.5" customHeight="1"/>
+    <row r="38" spans="1:6" ht="13.5" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>140</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E38" s="1">
         <v>10.847</v>
       </c>
     </row>
-    <row r="39" ht="13.5" customHeight="1">
+    <row r="39" spans="1:6" ht="13.5" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
-    <row r="40" ht="13.5" customHeight="1">
+    <row r="40" spans="1:6" ht="13.5" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
-    <row r="41" ht="13.5" customHeight="1">
+    <row r="41" spans="1:6" ht="13.5" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
-    <row r="42" ht="13.5" customHeight="1">
+    <row r="42" spans="1:6" ht="13.5" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
-    <row r="43" ht="13.5" customHeight="1">
+    <row r="43" spans="1:6" ht="13.5" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>164</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="13.5" customHeight="1">
+      <c r="A46" s="1" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="F46" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" ht="13.5" customHeight="1">
+    <row r="47" spans="1:6" ht="13.5" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
-    <row r="48" ht="13.5" customHeight="1"/>
+    <row r="48" spans="1:6" ht="13.5" customHeight="1"/>
     <row r="49" ht="13.5" customHeight="1"/>
     <row r="50" ht="13.5" customHeight="1"/>
     <row r="51" ht="13.5" customHeight="1"/>
